--- a/logs/one_head_map_search_optimization/experiments_summary.xlsx
+++ b/logs/one_head_map_search_optimization/experiments_summary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW80"/>
+  <dimension ref="A1:BW109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21417,10 +21417,8 @@
           <t>full</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="V80" t="n">
+        <v>2</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -21588,6 +21586,7635 @@
       </c>
       <c r="BW80" t="n">
         <v>0.01724275673372533</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46080.35921296296</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>02-27_08-37-16_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>5</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>2</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>[4, 2, -1, 0, 3, 1]</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>0.1816205001840344</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>70.91624715059457</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>0.4056434447760151</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>-0.1043349520367195</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>77.29154311336929</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>0.3512401711504492</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>77.29154311336929</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>77.29154311336929</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>0.3512401711504492</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>93.15750232234741</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>-0.08876912761028746</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV81" t="n">
+        <v>0.1098455778764769</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0.2023790788392494</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0.1098455778764769</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0.1098455778764769</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>0.2023790788392494</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>0.1063920934443811</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>0.2274558410284392</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0.1445388267833717</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>0.4992038360888842</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0.1445388267833717</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>0.1445388267833717</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>0.4992038360888842</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>0.3620709761346087</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>-0.2544986004592742</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>0.10404330295324</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>0.5822990477376515</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>0.10404330295324</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>0.10404330295324</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>0.5822990477376515</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>0.3162631534968413</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>-0.2696965266519353</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>308.8077447458624</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>0.1210787219360194</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>308.8077447458624</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>308.8077447458624</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>0.1210787219360194</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>371.8452830663129</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>-0.05833722435837752</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46080.43328703703</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>02-27_10-23-56_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>2</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>[4, 2, -1, 0, 3, 1]</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE82" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>0.2034866556197676</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>68.94976233830957</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0.3140324548144378</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>-0.02269102386101773</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>78.95744137773565</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>0.3245537268107864</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>78.95744137773565</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>78.95744137773565</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0.3245537268107864</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>93.98370235527119</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>-0.005663520728264676</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV82" t="n">
+        <v>0.08030983083297553</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0.4168467908713185</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0.08030983083297553</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0.08030983083297553</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0.4168467908713185</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0.1357441466098248</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>0.01432198405963614</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0.1769146275023933</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>0.387028601486094</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0.1769146275023933</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>0.1769146275023933</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>0.387028601486094</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>0.2972148573862118</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>-0.02978600109633578</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>0.151423232112986</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>0.3920836185231157</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>0.151423232112986</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>0.151423232112986</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>0.3920836185231157</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>0.2339191458169091</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>0.06088861861651074</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>315.4211178204932</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>0.1022558963626128</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>315.4211178204932</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>315.4211178204932</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>0.1022558963626128</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>375.2679312712723</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>-0.06807868449287624</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46080.48706018519</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>02-27_11-41-22_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>5</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [4, 2, -1, 0, 3, 1]}]</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>2</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>[4, 2, -1, 0, 3, 1]</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE83" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0.1917182298911868</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>56.00074635589297</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0.3457757813311274</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>-0.08408617395458323</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>67.74161086322484</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>0.3291206801763605</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>67.74161086322484</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>67.74161086322484</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0.3291206801763605</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>85.63666330212128</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>-0.09502453166576613</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV83" t="n">
+        <v>0.08620570586296293</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0.3740351150316643</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0.08620570586296293</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0.08620570586296293</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0.3740351150316643</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0.1451367106071569</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>-0.05388017475678764</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0.1834262050876799</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>0.3644673759089103</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0.1834262050876799</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>0.1834262050876799</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>0.3644673759089103</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>0.3622670317228635</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>-0.2551778911986302</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>0.1624115938663739</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>0.3479688217230172</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>0.1624115938663739</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>0.1624115938663739</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>0.3479688217230172</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>0.2735744047967906</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>-0.09831470315376145</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>270.5343999480821</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>0.2300114080418435</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>270.5343999480821</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>270.5343999480821</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>0.2300114080418435</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>341.7656750613571</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>0.02727464244611744</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46080.47609953704</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>02-27_11-25-35_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>5</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1, 2, 3, 4]}]</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>2</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>[0, 1, -1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE84" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0.1566724001821692</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>65.78230746904175</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0.4766929162366784</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0.2220920721808227</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>71.97008351458256</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0.4367662547431415</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>71.97008351458256</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>71.97008351458256</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0.4367662547431415</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>80.32521194869173</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0.1863957176514595</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV84" t="n">
+        <v>0.1091950492894194</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0.2071027574877763</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0.1091950492894194</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0.1091950492894194</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0.2071027574877763</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0.1459929833397102</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>-0.06009782192026303</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0.09358415658154808</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0.6757508853372802</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0.09358415658154808</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>0.09358415658154808</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>0.6757508853372802</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>0.1854457152944734</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>0.3574702043734215</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>0.07901805327945681</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>0.68276750964375</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>0.07901805327945681</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>0.07901805327945681</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>0.68276750964375</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>0.1590926825221606</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>0.3612932009920534</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>287.5985367991806</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>0.1814438665037613</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>287.5985367991806</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>287.5985367991806</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>0.1814438665037613</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>320.8103164136104</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>0.08691728716062774</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46080.54016203704</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>02-27_12-57-50_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>5</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [4, 2, -1, 0, 3, 1]}]</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>2</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>[4, 2, -1, 0, 3, 1]</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE85" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>0.1906893056931131</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>61.96001789070431</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>0.394979812608638</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>-0.2158413698943858</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>76.16208839444316</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>0.3971688820149618</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>76.16208839444316</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>76.16208839444316</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>0.3971688820149618</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>101.7547751516009</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>-0.2054241211917145</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV85" t="n">
+        <v>0.07939577635669358</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0.4234840082036628</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0.07939577635669358</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>0.07939577635669358</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>0.4234840082036628</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>0.1286706996893631</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>0.06568435437576148</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>0.1559379690919511</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>0.4597082426413925</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0.1559379690919511</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>0.1559379690919511</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>0.4597082426413925</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>0.4049471990374173</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>-0.4030555552276016</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>0.1067101058299943</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>0.5715926777023128</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>0.1067101058299943</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>0.1067101058299943</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>0.5715926777023128</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0.3308698165858902</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>-0.3283376588391087</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>304.306309726495</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>0.1338905995124718</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>304.306309726495</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>304.306309726495</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>0.1338905995124718</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>406.1546128910888</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>-0.1559876250759094</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46080.58657407408</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>02-27_14-04-40_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>2</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE86" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>0.1560444683980309</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>61.40773453414223</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>0.5604604982213968</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>-1.082213521570301</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>74.83590756745056</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>0.5034048620556313</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>74.83590756745056</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>74.83590756745056</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0.5034048620556313</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>87.51807921064027</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>-0.74864451496031</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV86" t="n">
+        <v>0.02361504454429825</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>0.8285242433349793</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>0.02361504454429825</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0.02361504454429825</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>0.8285242433349793</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>0.5451897408303904</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>-2.958782426157637</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0.1219222496987031</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>0.5775654451932488</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0.1219222496987031</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>0.1219222496987031</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>0.5775654451932488</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>0.2942900312671175</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>-0.01965210328391764</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>0.1348259300693595</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>0.4587165364700245</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>0.1348259300693595</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>0.1348259300693595</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>0.4587165364700245</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>0.2547873157626535</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>-0.02289048307374864</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>299.0632670454891</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>0.148813223224277</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>299.0632670454891</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>299.0632670454891</v>
+      </c>
+      <c r="BU86" t="n">
+        <v>0.148813223224277</v>
+      </c>
+      <c r="BV86" t="n">
+        <v>348.9780497547009</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>0.006746952674065776</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46080.58702546296</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>02-27_14-05-19_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" t="n">
+        <v>5</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>2</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>[4, 2, -1, 0, 3, 1]</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE87" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0.1616216596826262</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>58.98745892154236</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>0.5076140055295082</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0.1365917498174953</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>70.84619819618921</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>0.4920100773514656</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>70.84619819618921</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>70.84619819618921</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>0.4920100773514656</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>86.45364495505106</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>0.1388176454856068</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV87" t="n">
+        <v>0.07046864318754667</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0.4883065374247</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0.07046864318754667</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0.07046864318754667</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0.4883065374247</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0.1196836171986789</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>0.1309421931831459</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>0.1060440500805113</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>0.6325800155724808</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0.1060440500805113</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>0.1060440500805113</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>0.6325800155724808</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>0.229528979551083</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>0.2047311091164929</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>0.08644057809227941</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>0.6529684202790043</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>0.08644057809227941</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>0.08644057809227941</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>0.6529684202790043</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>0.1986988212745124</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>0.2022870813984917</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>283.1218395133962</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>0.1941853361296778</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>283.1218395133962</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>283.1218395133962</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>0.1941853361296778</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>345.2666684021813</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>0.01731019824429536</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46080.63797453704</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>02-27_15-18-41_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G88" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>2</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE88" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>0.2244155119396314</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>63.61561279293083</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>0.2932400623179503</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>-0.03739899982414802</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>75.42422944682491</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>0.2525387519030087</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>75.42422944682491</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>75.42422944682491</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>0.2525387519030087</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>91.54990852804747</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>-0.05291641053750673</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV88" t="n">
+        <v>0.06147094235777047</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0.5536414791029651</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0.06147094235777047</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0.06147094235777047</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>0.5536414791029651</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>0.1690249092005728</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>-0.2273393829952612</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>0.2367986667989396</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>0.1795431954770904</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0.2367986667989396</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>0.2367986667989396</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>0.1795431954770904</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>0.2887279858066082</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>-0.0003808037161068256</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>0.2156607736738792</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>0.1341902076128877</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>0.2156607736738792</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>0.2156607736738792</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>0.1341902076128877</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>0.2350492968672439</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>0.05635141961834667</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>301.1829874044677</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>0.1427801254190877</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>301.1829874044677</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>301.1829874044677</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>0.1427801254190877</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>365.5068319203147</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>-0.04029687505699719</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46080.67935185185</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>02-27_16-18-16_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>5</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>2</v>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE89" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>0.1803975340273927</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>71.8767265698814</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>0.4274224753739981</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>-0.3144462468723832</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>82.31944982309111</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>0.3776584518736765</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>82.31944982309111</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>82.31944982309111</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>0.3776584518736765</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>85.30720388849682</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>-0.2680833643604723</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV89" t="n">
+        <v>0.05436981973756758</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0.6052048107827432</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0.05436981973756758</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0.05436981973756758</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0.6052048107827432</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>0.1998565746296898</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>-0.4512171380756385</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0.1608853466764073</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>0.4425666359821047</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0.1608853466764073</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>0.1608853466764073</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>0.4425666359821047</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>0.3897494769600172</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>-0.3503986941894515</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>0.1496988919406597</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>0.3990062989029246</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>0.1496988919406597</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>0.1496988919406597</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>0.3990062989029246</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>0.3243397520714702</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>-0.3021215152855568</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>328.9128452340101</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>0.06385606182692793</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>328.9128452340101</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>328.9128452340101</v>
+      </c>
+      <c r="BU89" t="n">
+        <v>0.06385606182692793</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>340.314869750326</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>0.03140389010874634</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46080.68876157407</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>02-27_16-31-49_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>5</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]</t>
+        </is>
+      </c>
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>2</v>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>[4, 2, -1, 0, 3, 1]</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE90" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>0.1455898711049535</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>69.89133991905216</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>0.5298397218939508</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>0.2603376663780599</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>82.87040957220418</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>0.5126403810924145</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>82.87040957220418</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>82.87040957220418</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>0.5126403810924145</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>86.94969447303619</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>0.2874143614883239</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV90" t="n">
+        <v>0.06868653387988348</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0.5012469551917758</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>0.06868653387988348</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>0.06868653387988348</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>0.5012469551917758</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>0.143423898268007</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>-0.04144294257922487</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>0.08114294322909271</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>0.7188570323841731</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0.08114294322909271</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>0.08114294322909271</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>0.7188570323841731</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>0.128034340850367</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>0.556388354785452</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>0.05646134147889396</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>0.7733255727921005</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>0.05646134147889396</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>0.05646134147889396</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>0.7733255727921005</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>0.09376350624496692</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>0.6235691800020877</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>331.2753474702286</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>0.0571319640016128</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>331.2753474702286</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>331.2753474702286</v>
+      </c>
+      <c r="BU90" t="n">
+        <v>0.0571319640016128</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>347.4335561467826</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>0.01114285374497426</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46080.73048611111</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>02-27_17-31-54_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
+        <v>5</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>2</v>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE91" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>0.1403485013685158</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>46.60906832231584</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>0.6342502708059148</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>-0.8438471129475449</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>65.36162635714886</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>0.5844502648986322</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>65.36162635714886</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>65.36162635714886</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>0.5844502648986322</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>102.2902067322804</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>-0.34843047752257</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV91" t="n">
+        <v>0.02899222433017593</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>0.7894789656190051</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0.02899222433017593</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>0.02899222433017593</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>0.7894789656190051</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>0.2742806560702998</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>-0.9916321965858303</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>0.09160867924032035</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>0.6825954923982114</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0.09160867924032035</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>0.09160867924032035</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>0.6825954923982114</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>0.3398166319110563</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>-0.1773920508522537</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>0.09733539944859768</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>0.6092291585861345</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>0.09733539944859768</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>0.09733539944859768</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>0.6092291585861345</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>0.2646920883135943</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>-0.06265501196735079</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>261.2285691255764</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>0.2564974429911775</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>261.2285691255764</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>261.2285691255764</v>
+      </c>
+      <c r="BU91" t="n">
+        <v>0.2564974429911775</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>408.2820375528278</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>-0.1620426506848665</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46080.77131944444</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>02-27_18-30-42_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G92" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>5</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V92" t="n">
+        <v>2</v>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE92" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>0.151521547931784</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>62.3298528304539</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>0.5368747306979311</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>-0.1721197872931972</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>74.8826821990216</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>0.4896183104725645</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>74.8826821990216</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>74.8826821990216</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>0.4896183104725645</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>88.57811643459728</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>-0.07596654693223656</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV92" t="n">
+        <v>0.03648940791291724</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0.7350397192607958</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0.03648940791291724</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0.03648940791291724</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>0.7350397192607958</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>0.2451590326044923</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>-0.7801715571724332</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>0.1319322859385019</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>0.5428828075860148</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0.1319322859385019</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>0.1319322859385019</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>0.5428828075860148</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>0.2369302224757774</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>0.1790873831547737</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>0.1165080552048723</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>0.5322570100722286</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>0.1165080552048723</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>0.1165080552048723</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>0.5322570100722286</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>0.1734163922058571</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>0.3037880372286692</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>299.2457990470306</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>0.148293704971215</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>299.2457990470306</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>299.2457990470306</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>0.148293704971215</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>353.6569600911038</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>-0.006570050939954442</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46080.78950231482</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>02-27_18-56-53_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G93" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>5</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [4, 2, -1, 0, 3, 1]}]</t>
+        </is>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V93" t="n">
+        <v>2</v>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>[4, 2, -1, 0, 3, 1]</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z93" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE93" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>0.1480183087627958</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>66.64403370984815</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>0.5290647848788679</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>0.1817998324360986</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>78.67427507467418</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>0.5255128251315339</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>78.67427507467418</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>78.67427507467418</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>0.5255128251315339</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>85.59178882449142</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>0.1248226598004546</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV93" t="n">
+        <v>0.07195688557899897</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0.4774999734270531</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0.07195688557899897</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0.07195688557899897</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>0.4774999734270531</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0.1423593912511157</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>-0.03371324527316033</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>0.08173344660106675</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>0.7168110643211807</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0.08173344660106675</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>0.08173344660106675</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>0.7168110643211807</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>0.2097226993334984</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>0.2733556398052678</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>0.04910810664385881</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>0.8028464848125815</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>0.04910810664385881</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>0.04910810664385881</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>0.8028464848125815</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>0.1911634163942773</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>0.2325393485297179</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>314.4943018598715</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>0.1048937779653237</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>314.4943018598715</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>314.4943018598715</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>0.1048937779653237</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>341.8239097909888</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>0.02710889613998868</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46080.82211805556</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>02-27_19-43-51_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>5</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V94" t="n">
+        <v>2</v>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z94" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE94" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>0.1742221653692364</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>74.30959803460665</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>0.4485922871210335</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>-0.0005380002726944055</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>83.50315620771002</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>0.445681477867513</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>83.50315620771002</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>83.50315620771002</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>0.445681477867513</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>89.45160939089163</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>0.0109639844165117</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV94" t="n">
+        <v>0.0367873272815436</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0.7328764394471778</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0.0367873272815436</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0.0367873272815436</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0.7328764394471778</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0.1339467298902028</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>0.02737355342938175</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0.1536483898614288</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>0.467641145662216</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0.1536483898614288</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>0.1536483898614288</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>0.467641145662216</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>0.2783884910109464</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>0.03544333742077188</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>0.1165737333140264</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>0.5319933332380858</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0.1165737333140264</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>0.1165737333140264</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>0.5319933332380858</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>0.2496996279552207</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>-0.002465025772250495</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>333.7056153803834</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>0.05021499312256616</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>333.7056153803834</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>333.7056153803834</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>0.05021499312256616</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>357.1444027147102</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>-0.01649592741185901</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46080.86524305555</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>02-27_20-45-57_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>5</v>
+      </c>
+      <c r="K95" t="n">
+        <v>5</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V95" t="n">
+        <v>2</v>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z95" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE95" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>0.158117308886602</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>54.57705853425292</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>0.4921814766171204</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>0.1248808233614659</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>57.33967165961983</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>0.4845166461069995</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>57.33967165961983</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>57.33967165961983</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>0.4845166461069995</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>105.9273799987935</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>0.09492342588962183</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV95" t="n">
+        <v>0.08300861079002085</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0.397250158972588</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0.08300861079002085</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0.08300861079002085</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>0.397250158972588</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>0.09334933908509419</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>0.3221631014174408</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0.1032413540940006</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>0.6422907585602958</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0.1032413540940006</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>0.1032413540940006</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>0.6422907585602958</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>0.2673434258164813</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>0.07371212929235971</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>0.1119709303916477</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>0.5504721310961043</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>0.1119709303916477</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>0.1119709303916477</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>0.5504721310961043</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0.2022156013708899</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>0.1881683216757793</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>229.0604657432037</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>0.3480535357990087</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>229.0604657432037</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>229.0604657432037</v>
+      </c>
+      <c r="BU95" t="n">
+        <v>0.3480535357990087</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>423.1466116289001</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>-0.2043498488270956</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46080.89295138889</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>02-27_21-25-51_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V96" t="n">
+        <v>2</v>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z96" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE96" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>0.1911558051739656</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>54.00893486668306</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>0.403520653906857</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>0.1084543675020369</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>68.4137513262023</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>0.3395967741563113</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>68.4137513262023</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>68.4137513262023</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>0.3395967741563113</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>88.35458037738698</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>0.1082401107344886</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV96" t="n">
+        <v>0.07598479546869366</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0.4482521397073965</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0.07598479546869366</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0.07598479546869366</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>0.4482521397073965</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>0.1140892342774585</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>0.1715646464963566</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0.1791056472768328</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>0.3794371859300704</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0.1791056472768328</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>0.1791056472768328</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>0.3794371859300704</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>0.2536812839252259</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>0.1210485329578223</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>0.172279628155073</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>0.3083517853319327</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0.172279628155073</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>0.172279628155073</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>0.3083517853319327</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0.2130715982697427</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>0.1445849278993834</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>273.227635233909</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>0.2223459856558405</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>273.227635233909</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>273.227635233909</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>0.2223459856558405</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>352.8374793930744</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>-0.00423766441560236</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46080.91553240741</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>02-27_21-58-22_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>5</v>
+      </c>
+      <c r="K97" t="n">
+        <v>5</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>2</v>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z97" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE97" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>0.151731149009687</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>63.62331652401674</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>0.4831490114712571</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>-0.1584706215311631</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>64.92851468188832</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>0.4716230392892687</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>64.92851468188832</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>64.92851468188832</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>0.4716230392892687</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>89.90077218633354</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>-0.1704407007698497</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV97" t="n">
+        <v>0.115420226538659</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0.1618999217622358</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>0.115420226538659</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>0.115420226538659</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>0.1618999217622358</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>0.1337568270934473</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>0.0287524932702693</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>0.05917010743005444</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>0.7949882154253871</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0.05917010743005444</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>0.05917010743005444</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>0.7949882154253871</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>0.3848270503769327</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>-0.3333435374208313</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>0.08268054218430228</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>0.6680637751430125</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>0.08268054218430228</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>0.08268054218430228</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>0.6680637751430125</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>0.3377888439946939</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>-0.3561153653839064</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>259.4567878513999</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>0.2615402448264442</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>259.4567878513999</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>259.4567878513999</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>0.2615402448264442</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>358.7467160238684</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>-0.02105639354493261</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46080.9575462963</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>02-27_22-58-52_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>5</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V98" t="n">
+        <v>2</v>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z98" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE98" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0.1582358996074759</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>46.87322502205521</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>0.4971764381530165</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>-0.1885429027719839</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>54.39670730392152</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>0.4693323922505676</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>54.39670730392152</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>54.39670730392152</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>0.4693323922505676</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>105.8446841120463</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>-0.1465525438840263</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV98" t="n">
+        <v>0.1219058742087857</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0.1148057340036006</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0.1219058742087857</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0.1219058742087857</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>0.1148057340036006</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>0.1275183859560569</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>0.0740516419734415</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0.08567783053843638</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>0.7031446164276476</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0.08567783053843638</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>0.08567783053843638</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>0.7031446164276476</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>0.3393528915700281</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>-0.1757852896171856</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>0.08024281327938511</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>0.6778504856379589</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>0.08024281327938511</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>0.08024281327938511</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>0.6778504856379589</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>0.3192539084401467</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>-0.2817034617678214</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>217.2990026976587</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>0.3815287329330702</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>217.2990026976587</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>217.2990026976587</v>
+      </c>
+      <c r="BU98" t="n">
+        <v>0.3815287329330702</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>422.5926112622204</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>-0.2027730661245415</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46080.99295138889</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>02-27_23-49-51_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>5</v>
+      </c>
+      <c r="K99" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V99" t="n">
+        <v>2</v>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z99" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE99" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0.1484470872960162</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>37.85916077599158</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>0.5378170950994181</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0.06331755307604653</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>59.59755034859892</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0.4504672099222018</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>59.59755034859892</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>59.59755034859892</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>0.4504672099222018</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>87.77845888219629</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>0.05285694278387343</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV99" t="n">
+        <v>0.05939799987437527</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0.5686937217610923</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0.05939799987437527</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0.05939799987437527</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0.5686937217610923</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>0.1388003358813292</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>-0.007869901577491012</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0.1477160255036245</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>0.4881955211156997</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0.1477160255036245</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>0.1477160255036245</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>0.4881955211156997</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>0.2584114585540837</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>0.1046594881490387</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>0.1438516257374076</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>0.4224812232075438</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>0.1438516257374076</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>0.1438516257374076</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>0.4224812232075438</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0.221135695367686</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0.1122101287404137</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>238.0392357432802</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>0.3224983736044714</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>238.0392357432802</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>238.0392357432802</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>0.3224983736044714</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>350.4954880389807</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>0.00242805582353478</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46081.00600694444</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>02-28_00-08-39_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>5</v>
+      </c>
+      <c r="K100" t="n">
+        <v>5</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R100" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V100" t="n">
+        <v>2</v>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z100" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE100" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0.1544331381211744</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>68.77306857703614</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>0.4560671109956838</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>-0.1650597880206733</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>70.09974659980529</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>0.4551160827249615</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>70.09974659980529</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>70.09974659980529</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>0.4551160827249615</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>91.50015744045139</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>-0.1261441713517172</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV100" t="n">
+        <v>0.1147230133930522</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0.1669625906670292</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0.1147230133930522</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0.1147230133930522</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>0.1669625906670292</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0.09140619648734824</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>0.3362728290798842</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0.05929261301894031</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>0.7945637597248876</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0.05929261301894031</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>0.05929261301894031</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>0.7945637597248876</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>0.3831406077666935</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>-0.3275003739701563</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>0.08561970739058888</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>0.6562639565033253</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>0.08561970739058888</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>0.08561970739058888</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>0.6562639565033253</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0.3671627940075382</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>-0.4740424836491346</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>280.1393510654185</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>0.2026740240046045</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>280.1393510654185</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>280.1393510654185</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>0.2026740240046045</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>365.1589201635439</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>-0.03930665686746915</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46081.04891203704</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>02-28_01-10-26_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" t="n">
+        <v>5</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V101" t="n">
+        <v>2</v>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z101" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE101" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0.1825513574138678</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>57.29223138563908</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0.460966129529242</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>-0.05780922031189531</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>59.4145955572853</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>0.463004672819086</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>59.4145955572853</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>59.4145955572853</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>0.463004672819086</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>97.23978132452609</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>0.02786904653194031</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV101" t="n">
+        <v>0.09544278307346178</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0.3069619913256181</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0.09544278307346178</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0.09544278307346178</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>0.3069619913256181</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0.149179518002217</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>-0.08323618362725371</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0.09743947342447444</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>0.662393035902864</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0.09743947342447444</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>0.09743947342447444</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>0.662393035902864</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>0.2422831404881217</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>0.1605406655289933</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>0.1100412617154038</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>0.5582191404733455</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>0.1100412617154038</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>0.1100412617154038</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>0.5582191404733455</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0.2143397449819553</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>0.1394937199670706</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>237.3554587109279</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>0.3244445235745135</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>237.3554587109279</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>237.3554587109279</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>0.3244445235745135</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>388.3533228946329</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>-0.1053220157410506</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46081.09657407407</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>02-28_02-19-04_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>5</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V102" t="n">
+        <v>2</v>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z102" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE102" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0.1436889478345</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>60.86503424834324</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>0.4966210037372577</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>-0.04841848321354761</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>62.29767520977671</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0.4854692757924192</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>62.29767520977671</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>62.29767520977671</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>0.4854692757924192</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>94.93761970579962</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>-0.03275066498746476</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV102" t="n">
+        <v>0.1136577914527471</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0.1746974792414442</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0.1136577914527471</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0.1136577914527471</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>0.1746974792414442</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0.1266365236904711</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>0.08045510223293817</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0.05974340260903654</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>0.7930018700757513</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0.05974340260903654</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>0.05974340260903654</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>0.7930018700757513</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>0.2980544648361175</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>-0.03269506158521129</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>0.07903488437760853</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>0.6826999381083794</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>0.07903488437760853</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>0.07903488437760853</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>0.6826999381083794</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>0.273972870294702</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>-0.09991441609247942</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>248.938264760667</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>0.291477815744106</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>248.938264760667</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>248.938264760667</v>
+      </c>
+      <c r="BU102" t="n">
+        <v>0.291477815744106</v>
+      </c>
+      <c r="BV102" t="n">
+        <v>379.0518149643776</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>-0.07884828450509929</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46081.09246527778</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>02-28_02-13-09_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>5</v>
+      </c>
+      <c r="K103" t="n">
+        <v>5</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 3, 1, -1, 4, 2]}]</t>
+        </is>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V103" t="n">
+        <v>2</v>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>[0, 3, 1, -1, 4, 2]</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z103" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE103" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>0.192828678664556</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>58.67890427100014</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0.4083677169578576</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>-0.2914973372308741</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>74.05045418428311</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0.3223995332587254</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>74.05045418428311</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>74.05045418428311</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0.3223995332587254</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>96.84327660387352</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>-0.009066207224506989</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV103" t="n">
+        <v>0.06121758391647709</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0.5554811889687143</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0.06121758391647709</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0.06121758391647709</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>0.5554811889687143</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0.1402038664521982</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>-0.01806134822883143</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0.1949795806001175</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>0.3244373973514876</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0.1949795806001175</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>0.1949795806001175</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>0.3244373973514876</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>0.3098167299334355</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>-0.07344879793918691</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>0.1864499862538397</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>0.2514622796766431</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>0.1864499862538397</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>0.1864499862538397</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>0.2514622796766431</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0.2102536229946458</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0.1558982072979503</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>295.7591695863626</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>0.1582172670380529</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>295.7591695863626</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>295.7591695863626</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>0.1582172670380529</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>386.7128321961131</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>-0.1006528900279577</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46081.181875</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>02-28_04-21-54_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]</t>
+        </is>
+      </c>
+      <c r="R104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V104" t="n">
+        <v>1</v>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>[-1, 0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z104" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE104" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0.1319241736700933</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>55.02183833585558</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0.5398285515638945</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>-0.01889123890826724</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>59.9589075840741</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0.5442298931271269</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>59.9589075840741</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>59.9589075840741</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0.5442298931271269</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>86.98373926487903</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>-0.01870908161135032</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV104" t="n">
+        <v>0.1225787537222603</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0.1099197587304653</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0.1225787537222603</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0.1225787537222603</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0.1099197587304653</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0.1314588505436572</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>0.0454387742101402</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0.02175722483140013</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>0.924615862911028</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0.02175722483140013</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>0.02175722483140013</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>0.924615862911028</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>0.2893738071590652</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>-0.002618436766547383</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>0.04372369811652178</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>0.824463181951166</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>0.04372369811652178</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>0.04372369811652178</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>0.824463181951166</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>0.2813100480866159</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>-0.1293708641637019</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>239.6475706596269</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>0.3179207689158531</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>239.6475706596269</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>239.6475706596269</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>0.3179207689158531</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>347.2328143537262</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>0.01171420027470327</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46081.18601851852</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>02-28_04-27-52_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G105" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>5</v>
+      </c>
+      <c r="K105" t="n">
+        <v>5</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V105" t="n">
+        <v>2</v>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z105" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE105" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0.1582379246500467</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>64.75654785332361</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>0.474069957344906</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0.1328389436947289</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>68.19429061306248</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>0.4821729767480963</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>68.19429061306248</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>68.19429061306248</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>0.4821729767480963</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>86.2205667856979</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0.1405425720418001</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV105" t="n">
+        <v>0.1042690541246682</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0.2428718514913649</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0.1042690541246682</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0.1042690541246682</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>0.2428718514913649</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>0.1319396798306705</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>0.04194733189409294</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0.07063758764641591</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>0.7552558457231784</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0.07063758764641591</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>0.07063758764641591</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>0.7552558457231784</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>0.2257452622832222</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>0.2178408813156881</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>0.07317387964054162</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>0.7062300182807404</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>0.07317387964054162</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>0.07317387964054162</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>0.7062300182807404</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>0.1787311244615289</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>0.282451068282083</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>272.5290819308391</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0.2243341914971003</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>272.5290819308391</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>272.5290819308391</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>0.2243341914971003</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>344.3458510762167</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>0.01993100667533487</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46081.23357638889</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>02-28_05-36-21_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>5</v>
+      </c>
+      <c r="K106" t="n">
+        <v>5</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'rev', 'map': [-1, 0, 1, 2, 3, 4]}]</t>
+        </is>
+      </c>
+      <c r="R106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="V106" t="n">
+        <v>1</v>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>[-1, 0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z106" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE106" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0.1333293240572715</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>31.45391411428179</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>0.631316218219116</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>0.02458713338765672</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>36.33778212436339</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>0.6312411342556508</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>36.33778212436339</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>36.33778212436339</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>0.6312411342556508</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>86.59889370593321</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>0.02109070179308023</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV106" t="n">
+        <v>0.1240336012250068</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0.09935568480302837</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0.1240336012250068</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>0.1240336012250068</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>0.09935568480302837</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0.1403900998681363</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>-0.01941364362062692</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0.01869790422116057</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>0.9352157554096604</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0.01869790422116057</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>0.01869790422116057</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>0.9352157554096604</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>0.2534650851622633</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>0.1217976154953209</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>0.02400850172608245</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>0.9036134595046074</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>0.02400850172608245</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>0.02400850172608245</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>0.9036134595046074</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>0.2575476379425731</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>-0.03397230353096226</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>145.1843884902815</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0.5867796373053062</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>145.1843884902815</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>145.1843884902815</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>0.5867796373053062</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>345.7441720007604</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>0.01595113882857802</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46081.27094907407</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>02-28_06-30-10_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>5</v>
+      </c>
+      <c r="K107" t="n">
+        <v>5</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V107" t="n">
+        <v>2</v>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z107" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE107" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0.1447492343664284</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>65.18463826366163</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>0.5244981900219139</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0.1545537520794397</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>72.68354958091244</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>0.4985773470353754</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>72.68354958091244</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>72.68354958091244</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>0.4985773470353754</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>83.09692053425687</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0.1008259193665001</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV107" t="n">
+        <v>0.08792712107693769</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0.3615354148597131</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>0.08792712107693769</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>0.08792712107693769</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>0.3615354148597131</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>0.1158252254392688</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>0.1589591060970228</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>0.08021477448968645</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>0.72207293882607</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0.08021477448968645</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>0.08021477448968645</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>0.72207293882607</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>0.2445120853262197</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>0.1528178477275042</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>0.06538070065015959</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>0.7375171669297647</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>0.06538070065015959</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>0.06538070065015959</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>0.7375171669297647</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>0.2401555192811114</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>0.03585155173454457</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>290.5006757274335</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>0.1731838675259557</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>290.5006757274335</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>290.5006757274335</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>0.1731838675259557</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>331.7871893069825</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>0.05567517190691784</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46081.34688657407</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>02-28_08-19-31_multihead_spsa_serial_f5_w5_h5_effsu2_full_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>5</v>
+      </c>
+      <c r="K108" t="n">
+        <v>5</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 2, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [1, 3, 0, 4, 2, -1]}]</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V108" t="n">
+        <v>2</v>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>[1, 3, 0, 4, 2, -1]</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z108" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE108" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>0.1469721828426408</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>63.96725806070077</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>0.5207696817741297</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>0.175748525471228</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>68.64132892476847</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>0.5112843385538525</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>68.64132892476847</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>68.64132892476847</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>0.5112843385538525</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>86.98444636215098</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0.1407249303282233</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV108" t="n">
+        <v>0.08429104276707121</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0.3879380446878311</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0.08429104276707121</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0.08429104276707121</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>0.3879380446878311</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>0.09969395434080076</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>0.2760929913365602</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0.08155816432975518</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>0.7174183799541352</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0.08155816432975518</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>0.08155816432975518</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>0.7174183799541352</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>0.2420384168950972</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>0.1613885805102661</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>0.06960147718683854</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>0.7205720841746572</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>0.06960147718683854</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>0.06960147718683854</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>0.7205720841746572</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>0.2206625279702122</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>0.1141097461775222</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>274.3298650147906</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>0.2192088453987855</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>274.3298650147906</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>274.3298650147906</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>0.2192088453987855</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>347.3753905493963</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>0.0113084032885461</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46081.41501157408</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>02-28_09-57-37_multihead_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>['wv', 'sv', 'yr', 'ya', 'rarad']</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>5</v>
+      </c>
+      <c r="K109" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 1, 2, 3, 4]}]</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>[-1, 0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z109" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE109" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0.1020014350609924</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>9.140938992070106</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>0.6984763485481105</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>0.3434421345944883</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>12.70246903510684</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>0.6990263428496168</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>12.70246903510684</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>12.70246903510684</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>0.6990263428496168</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>103.7401829007103</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>0.3279838519733189</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV109" t="n">
+        <v>0.1244835438248152</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0.09608851977129451</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0.1244835438248152</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>0.1244835438248152</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>0.09608851977129451</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0.1230062814092715</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>0.1068153549471912</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0.01289019189679517</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>0.95533823819071</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0.01289019189679517</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>0.01289019189679517</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>0.95533823819071</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>0.060805164615609</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>0.7893230914962421</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>0.02769267488657426</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>0.8888226695762211</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>0.02769267488657426</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>0.02769267488657426</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>0.8888226695762211</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>0.1006209261625602</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0.5960388080479331</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>50.64480972981899</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0.8558559438602421</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>50.64480972981899</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>50.64480972981899</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>0.8558559438602421</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>414.6762992306536</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>-0.1802418465980882</v>
       </c>
     </row>
   </sheetData>
